--- a/data/agiliberti.xlsx
+++ b/data/agiliberti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/Resumen/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{4D46B017-80C7-4E3B-841A-986BBC50232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37F63784-E8D5-491A-906A-15886F889326}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{4D46B017-80C7-4E3B-841A-986BBC50232E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D282858A-A32B-4C7C-ABB4-E5BBF7EE3807}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -3186,7 +3186,7 @@
         <v>46097.859999999993</v>
       </c>
       <c r="I59" s="5">
-        <f t="shared" ref="I59:I60" si="71">+G59*0.1</f>
+        <f t="shared" ref="I59" si="71">+G59*0.1</f>
         <v>121.21199999999999</v>
       </c>
       <c r="J59" s="5">
@@ -3194,7 +3194,7 @@
         <v>4609.7860000000001</v>
       </c>
       <c r="K59" s="5">
-        <f t="shared" ref="K59:K60" si="73">+G59-I59</f>
+        <f t="shared" ref="K59" si="73">+G59-I59</f>
         <v>1090.9079999999999</v>
       </c>
       <c r="L59" s="5">
@@ -3202,11 +3202,11 @@
         <v>41488.073999999986</v>
       </c>
       <c r="M59" s="5">
-        <f t="shared" ref="M59:M60" si="75">+K59/30</f>
+        <f t="shared" ref="M59" si="75">+K59/30</f>
         <v>36.363599999999998</v>
       </c>
       <c r="N59" s="6">
-        <f t="shared" ref="N59:N60" si="76">+G59/D59</f>
+        <f t="shared" ref="N59" si="76">+G59/D59</f>
         <v>3.156795478082941E-2</v>
       </c>
     </row>
@@ -3267,35 +3267,219 @@
         <v>14</v>
       </c>
       <c r="D61" s="4">
-        <f t="shared" ref="D61" si="84">+D60+K60+E60-F61</f>
+        <f t="shared" ref="D61:D64" si="84">+D60+K60+E60-F61</f>
         <v>40548.480999999985</v>
+      </c>
+      <c r="G61" s="2">
+        <v>567.67999999999995</v>
       </c>
       <c r="H61" s="5">
         <f t="shared" si="77"/>
-        <v>47276.09</v>
+        <v>47843.77</v>
       </c>
       <c r="I61" s="5">
         <f t="shared" si="78"/>
-        <v>0</v>
+        <v>56.768000000000001</v>
       </c>
       <c r="J61" s="5">
         <f t="shared" si="79"/>
-        <v>4727.6090000000004</v>
+        <v>4784.3770000000004</v>
       </c>
       <c r="K61" s="5">
         <f t="shared" si="80"/>
-        <v>0</v>
+        <v>510.91199999999992</v>
       </c>
       <c r="L61" s="5">
         <f t="shared" si="81"/>
-        <v>42548.480999999985</v>
+        <v>43059.392999999982</v>
       </c>
       <c r="M61" s="5">
         <f t="shared" si="82"/>
-        <v>0</v>
+        <v>17.030399999999997</v>
       </c>
       <c r="N61" s="6">
         <f t="shared" si="83"/>
+        <v>1.4000031221884739E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A62" s="3">
+        <v>45902</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D62" s="4">
+        <f t="shared" si="84"/>
+        <v>41059.392999999982</v>
+      </c>
+      <c r="G62" s="2">
+        <v>944.36</v>
+      </c>
+      <c r="H62" s="5">
+        <f t="shared" ref="H62:H64" si="85">+H61+G62</f>
+        <v>48788.13</v>
+      </c>
+      <c r="I62" s="5">
+        <f t="shared" ref="I62:I64" si="86">+G62*0.1</f>
+        <v>94.436000000000007</v>
+      </c>
+      <c r="J62" s="5">
+        <f t="shared" ref="J62:J64" si="87">+J61+I62</f>
+        <v>4878.8130000000001</v>
+      </c>
+      <c r="K62" s="5">
+        <f t="shared" ref="K62:K64" si="88">+G62-I62</f>
+        <v>849.92399999999998</v>
+      </c>
+      <c r="L62" s="5">
+        <f t="shared" ref="L62:L64" si="89">+L61+K62</f>
+        <v>43909.316999999981</v>
+      </c>
+      <c r="M62" s="5">
+        <f t="shared" ref="M62:M64" si="90">+K62/30</f>
+        <v>28.3308</v>
+      </c>
+      <c r="N62" s="6">
+        <f t="shared" ref="N62:N64" si="91">+G62/D62</f>
+        <v>2.299985292037806E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A63" s="3">
+        <v>45932</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63" s="4">
+        <f t="shared" si="84"/>
+        <v>41909.316999999981</v>
+      </c>
+      <c r="G63" s="2">
+        <v>880.06</v>
+      </c>
+      <c r="H63" s="5">
+        <f t="shared" si="85"/>
+        <v>49668.189999999995</v>
+      </c>
+      <c r="I63" s="5">
+        <f t="shared" si="86"/>
+        <v>88.006</v>
+      </c>
+      <c r="J63" s="5">
+        <f t="shared" si="87"/>
+        <v>4966.8190000000004</v>
+      </c>
+      <c r="K63" s="5">
+        <f t="shared" si="88"/>
+        <v>792.05399999999997</v>
+      </c>
+      <c r="L63" s="5">
+        <f t="shared" si="89"/>
+        <v>44701.370999999977</v>
+      </c>
+      <c r="M63" s="5">
+        <f t="shared" si="90"/>
+        <v>26.401799999999998</v>
+      </c>
+      <c r="N63" s="6">
+        <f t="shared" si="91"/>
+        <v>2.0999149186802551E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A64" s="3">
+        <v>45963</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D64" s="4">
+        <f t="shared" si="84"/>
+        <v>42701.370999999977</v>
+      </c>
+      <c r="G64" s="2">
+        <v>1537.25</v>
+      </c>
+      <c r="H64" s="5">
+        <f t="shared" si="85"/>
+        <v>51205.439999999995</v>
+      </c>
+      <c r="I64" s="5">
+        <f t="shared" si="86"/>
+        <v>153.72500000000002</v>
+      </c>
+      <c r="J64" s="5">
+        <f t="shared" si="87"/>
+        <v>5120.5440000000008</v>
+      </c>
+      <c r="K64" s="5">
+        <f t="shared" si="88"/>
+        <v>1383.5250000000001</v>
+      </c>
+      <c r="L64" s="5">
+        <f t="shared" si="89"/>
+        <v>46084.895999999979</v>
+      </c>
+      <c r="M64" s="5">
+        <f t="shared" si="90"/>
+        <v>46.1175</v>
+      </c>
+      <c r="N64" s="6">
+        <f t="shared" si="91"/>
+        <v>3.6000015081482997E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A65" s="3">
+        <v>45994</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D65" s="4">
+        <f t="shared" ref="D65" si="92">+D64+K64+E64-F65</f>
+        <v>44084.895999999979</v>
+      </c>
+      <c r="H65" s="5">
+        <f t="shared" ref="H65" si="93">+H64+G65</f>
+        <v>51205.439999999995</v>
+      </c>
+      <c r="I65" s="5">
+        <f t="shared" ref="I65" si="94">+G65*0.1</f>
+        <v>0</v>
+      </c>
+      <c r="J65" s="5">
+        <f t="shared" ref="J65" si="95">+J64+I65</f>
+        <v>5120.5440000000008</v>
+      </c>
+      <c r="K65" s="5">
+        <f t="shared" ref="K65" si="96">+G65-I65</f>
+        <v>0</v>
+      </c>
+      <c r="L65" s="5">
+        <f t="shared" ref="L65" si="97">+L64+K65</f>
+        <v>46084.895999999979</v>
+      </c>
+      <c r="M65" s="5">
+        <f t="shared" ref="M65" si="98">+K65/30</f>
+        <v>0</v>
+      </c>
+      <c r="N65" s="6">
+        <f t="shared" ref="N65" si="99">+G65/D65</f>
         <v>0</v>
       </c>
     </row>

--- a/data/agiliberti.xlsx
+++ b/data/agiliberti.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\OneDrive\Documentos\Proyectos\FIFI\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d3c7c81f20a53ce1/Documentos/Proyectos/FIFI/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9123FF-FA1F-4189-8032-EF2A6AB6C513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{DA9123FF-FA1F-4189-8032-EF2A6AB6C513}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DB95E5E-733F-470B-A1A6-0F4A9750A940}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="17">
   <si>
     <t>Fecha</t>
   </si>
@@ -446,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -3592,33 +3592,174 @@
         <f t="shared" si="100"/>
         <v>46316.211999999978</v>
       </c>
+      <c r="G68" s="2">
+        <v>598</v>
+      </c>
       <c r="H68" s="5">
         <f t="shared" ref="H68" si="108">+H67+G68</f>
-        <v>53684.679999999993</v>
+        <v>54282.679999999993</v>
       </c>
       <c r="I68" s="5">
         <f t="shared" ref="I68" si="109">+G68*0.1</f>
-        <v>0</v>
+        <v>59.800000000000004</v>
       </c>
       <c r="J68" s="5">
         <f t="shared" ref="J68" si="110">+J67+I68</f>
-        <v>5368.4680000000008</v>
+        <v>5428.2680000000009</v>
       </c>
       <c r="K68" s="5">
         <f t="shared" ref="K68" si="111">+G68-I68</f>
-        <v>0</v>
+        <v>538.20000000000005</v>
       </c>
       <c r="L68" s="5">
         <f t="shared" ref="L68" si="112">+L67+K68</f>
-        <v>48316.211999999978</v>
+        <v>48854.411999999975</v>
       </c>
       <c r="M68" s="5">
         <f t="shared" ref="M68" si="113">+K68/30</f>
-        <v>0</v>
+        <v>17.940000000000001</v>
       </c>
       <c r="N68" s="6">
         <f t="shared" ref="N68" si="114">+G68/D68</f>
-        <v>0</v>
+        <v>1.2911245850588997E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A69" s="3">
+        <v>46118</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69" s="4">
+        <f t="shared" ref="D69:D71" si="115">+D68+K68+E68-F69</f>
+        <v>46854.411999999975</v>
+      </c>
+      <c r="G69" s="2">
+        <v>312</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" ref="H69:H71" si="116">+H68+G69</f>
+        <v>54594.679999999993</v>
+      </c>
+      <c r="I69" s="5">
+        <f t="shared" ref="I69:I71" si="117">+G69*0.1</f>
+        <v>31.200000000000003</v>
+      </c>
+      <c r="J69" s="5">
+        <f t="shared" ref="J69:J71" si="118">+J68+I69</f>
+        <v>5459.4680000000008</v>
+      </c>
+      <c r="K69" s="5">
+        <f t="shared" ref="K69:K71" si="119">+G69-I69</f>
+        <v>280.8</v>
+      </c>
+      <c r="L69" s="5">
+        <f t="shared" ref="L69:L71" si="120">+L68+K69</f>
+        <v>49135.211999999978</v>
+      </c>
+      <c r="M69" s="5">
+        <f t="shared" ref="M69:M71" si="121">+K69/30</f>
+        <v>9.3600000000000012</v>
+      </c>
+      <c r="N69" s="6">
+        <f t="shared" ref="N69:N71" si="122">+G69/D69</f>
+        <v>6.658924670743924E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A70" s="3">
+        <v>46149</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="4">
+        <f t="shared" si="115"/>
+        <v>47135.211999999978</v>
+      </c>
+      <c r="G70" s="2">
+        <v>1123.47</v>
+      </c>
+      <c r="H70" s="5">
+        <f t="shared" si="116"/>
+        <v>55718.149999999994</v>
+      </c>
+      <c r="I70" s="5">
+        <f t="shared" si="117"/>
+        <v>112.34700000000001</v>
+      </c>
+      <c r="J70" s="5">
+        <f t="shared" si="118"/>
+        <v>5571.8150000000005</v>
+      </c>
+      <c r="K70" s="5">
+        <f t="shared" si="119"/>
+        <v>1011.123</v>
+      </c>
+      <c r="L70" s="5">
+        <f t="shared" si="120"/>
+        <v>50146.334999999977</v>
+      </c>
+      <c r="M70" s="5">
+        <f t="shared" si="121"/>
+        <v>33.704100000000004</v>
+      </c>
+      <c r="N70" s="6">
+        <f t="shared" si="122"/>
+        <v>2.3835047140553872E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A71" s="3">
+        <v>46180</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="4">
+        <f t="shared" si="115"/>
+        <v>48146.334999999977</v>
+      </c>
+      <c r="G71" s="2">
+        <v>878.65</v>
+      </c>
+      <c r="H71" s="5">
+        <f t="shared" si="116"/>
+        <v>56596.799999999996</v>
+      </c>
+      <c r="I71" s="5">
+        <f t="shared" si="117"/>
+        <v>87.865000000000009</v>
+      </c>
+      <c r="J71" s="5">
+        <f t="shared" si="118"/>
+        <v>5659.68</v>
+      </c>
+      <c r="K71" s="5">
+        <f t="shared" si="119"/>
+        <v>790.78499999999997</v>
+      </c>
+      <c r="L71" s="5">
+        <f t="shared" si="120"/>
+        <v>50937.119999999981</v>
+      </c>
+      <c r="M71" s="5">
+        <f t="shared" si="121"/>
+        <v>26.359500000000001</v>
+      </c>
+      <c r="N71" s="6">
+        <f t="shared" si="122"/>
+        <v>1.8249571852146179E-2</v>
       </c>
     </row>
   </sheetData>
